--- a/medical_surveys_questionnaires/048_upper_respiratory_infection_assessment--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/048_upper_respiratory_infection_assessment--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1006,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>runny_nose</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shortness of Breath</t>
+          <t>Runny Nose</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>stuffy_nose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>Stuffy Nose</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>runny_nose</t>
+          <t>runny_eyes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Runny Nose</t>
+          <t>Runny Eyes</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stuffy_nose</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stuffy Nose</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>runny_eyes</t>
+          <t>dizziness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Runny Eyes</t>
+          <t>Dizziness</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>headache</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dizziness</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dizziness</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nausea</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nausea</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vomiting</t>
+          <t>abdominal_pain</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vomiting</t>
+          <t>Abdominal Pain</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>abdominal_distress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Abdominal Distress</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>abdominal_pain</t>
+          <t>chest_tightness</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Abdominal Pain</t>
+          <t>Chest Tightness</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>abdominal_distress</t>
+          <t>chest_pain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Abdominal Distress</t>
+          <t>Chest Pain</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chest_tightness</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chest Tightness</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chest_pain</t>
+          <t>muscle_aches</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chest Pain</t>
+          <t>Muscle Aches</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>back_pain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Back Pain</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>muscle_aches</t>
+          <t>joint_pain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Muscle Aches</t>
+          <t>Joint Pain</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>back_pain</t>
+          <t>joint_swelling</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Back Pain</t>
+          <t>Joint Swelling</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>joint_pain</t>
+          <t>skin_rash</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Joint Pain</t>
+          <t>Skin Rash</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>joint_swelling</t>
+          <t>skin_lesions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Joint Swelling</t>
+          <t>Skin Lesions</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>skin_rash</t>
+          <t>general_malaise</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Skin Rash</t>
+          <t>General Malaise</t>
         </is>
       </c>
     </row>
@@ -1430,63 +1430,63 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>skin_lesions</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Skin Lesions</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>respiratory_system_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>general_malaise</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>General Malaise</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>respiratory_system_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>less_than_2_weeks_ago</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fever</t>
+          <t>Less than 2 weeks ago</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>respiratory_system_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>less_than_4_weeks_ago</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>Less than 4 weeks ago</t>
         </is>
       </c>
     </row>
@@ -1498,80 +1498,80 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>more_than_4_weeks_ago</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>More than 4 weeks ago</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>recent_contacts_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>less_than_2_weeks_ago</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Less than 2 weeks ago</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>recent_contacts_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>less_than_2_weeks_ago</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Less than 2 weeks ago</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>recent_contacts_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>less_than_4_weeks_ago</t>
+          <t>coworker</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Less than 4 weeks ago</t>
+          <t>Coworker</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>recent_contacts_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>more_than_4_weeks_ago</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>More than 4 weeks ago</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>community</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Community</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>coworker</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coworker</t>
+          <t>Travel</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>healthcare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -1651,80 +1651,80 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>recent_contacts_choices</t>
+          <t>travel_history_duration_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>recent_contacts_choices</t>
+          <t>travel_history_duration_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>less_than_2_days</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Less than 2 days</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>recent_contacts_choices</t>
+          <t>travel_history_duration_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>healthcare</t>
+          <t>2-7_days</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>2-7 days</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>recent_contacts_choices</t>
+          <t>travel_history_duration_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2-4_weeks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2-4 weeks</t>
         </is>
       </c>
     </row>
@@ -1753,80 +1753,80 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>less_than_2_days</t>
+          <t>more_than_4_weeks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Less than 2 days</t>
+          <t>More than 4 weeks</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>travel_history_duration_choices</t>
+          <t>recent_contacts_duration_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2-7_days</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2-7 days</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>travel_history_duration_choices</t>
+          <t>recent_contacts_duration_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1-2_weeks</t>
+          <t>less_than_2_days</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1-2 weeks</t>
+          <t>Less than 2 days</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>travel_history_duration_choices</t>
+          <t>recent_contacts_duration_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2-4_weeks</t>
+          <t>2-7_days</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2-4 weeks</t>
+          <t>2-7 days</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>travel_history_duration_choices</t>
+          <t>recent_contacts_duration_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>more_than_4_weeks</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>More than 4 weeks</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2-4_weeks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2-4 weeks</t>
         </is>
       </c>
     </row>
@@ -1855,80 +1855,80 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>less_than_2_days</t>
+          <t>more_than_4_weeks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Less than 2 days</t>
+          <t>More than 4 weeks</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>recent_contacts_duration_choices</t>
+          <t>recent_contact_location_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2-7_days</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2-7 days</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>recent_contacts_duration_choices</t>
+          <t>recent_contact_location_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1-2_weeks</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1-2 weeks</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>recent_contacts_duration_choices</t>
+          <t>recent_contact_location_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2-4_weeks</t>
+          <t>community</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2-4 weeks</t>
+          <t>Community</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>recent_contacts_duration_choices</t>
+          <t>recent_contact_location_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>more_than_4_weeks</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>More than 4 weeks</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -1957,80 +1957,80 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>recent_contact_location_choices</t>
+          <t>healthcare_contacts_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>recent_contact_location_choices</t>
+          <t>healthcare_contacts_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>recent_contact_location_choices</t>
+          <t>healthcare_contacts_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>healthcare_provider</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Healthcare Provider</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>recent_contact_location_choices</t>
+          <t>healthcare_contacts_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -2042,80 +2042,80 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>healthcare_contacts_choices</t>
+          <t>healthcare_contacts_duration_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>healthcare_contacts_choices</t>
+          <t>healthcare_contacts_duration_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>healthcare_provider</t>
+          <t>less_than_2_days</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Healthcare Provider</t>
+          <t>Less than 2 days</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>healthcare_contacts_choices</t>
+          <t>healthcare_contacts_duration_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>2-7_days</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>2-7 days</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>healthcare_contacts_choices</t>
+          <t>healthcare_contacts_duration_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2-4_weeks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2-4 weeks</t>
         </is>
       </c>
     </row>
@@ -2144,87 +2144,87 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>less_than_2_days</t>
+          <t>more_than_4_weeks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Less than 2 days</t>
+          <t>More than 4 weeks</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>healthcare_contacts_duration_choices</t>
+          <t>healthcare_contact_frequency_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2-7_days</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2-7 days</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>healthcare_contacts_duration_choices</t>
+          <t>healthcare_contact_frequency_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1-2_weeks</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1-2 weeks</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>healthcare_contacts_duration_choices</t>
+          <t>healthcare_contact_frequency_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2-4_weeks</t>
+          <t>twice</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2-4 weeks</t>
+          <t>Twice</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>healthcare_contacts_duration_choices</t>
+          <t>healthcare_contact_frequency_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>more_than_4_weeks</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>More than 4 weeks</t>
+          <t>Multiple</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>healthcare_contact_frequency_choices</t>
+          <t>travel_type_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2241,58 +2241,58 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>healthcare_contact_frequency_choices</t>
+          <t>travel_type_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>once</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Once</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>healthcare_contact_frequency_choices</t>
+          <t>travel_type_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>twice</t>
+          <t>interstate</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Interstate</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>healthcare_contact_frequency_choices</t>
+          <t>travel_type_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>international</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Multiple</t>
+          <t>International</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>travel_type_choices</t>
+          <t>travel_mode_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2309,51 +2309,51 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>travel_type_choices</t>
+          <t>travel_mode_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>by_car</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>By Car</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>travel_type_choices</t>
+          <t>travel_mode_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>interstate</t>
+          <t>by_air</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Interstate</t>
+          <t>By Air</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>travel_type_choices</t>
+          <t>travel_mode_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>by_train</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>By Train</t>
         </is>
       </c>
     </row>
@@ -2365,87 +2365,87 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>by_other</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>By Other</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>travel_accommodation_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>by_car</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>By Car</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>travel_accommodation_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>by_air</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>By Air</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>travel_accommodation_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>by_train</t>
+          <t>hostel</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>By Train</t>
+          <t>Hostel</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>travel_mode_choices</t>
+          <t>travel_accommodation_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>by_other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>By Other</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>travel_accommodation_choices</t>
+          <t>travel_food_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2462,58 +2462,58 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>travel_accommodation_choices</t>
+          <t>travel_food_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>self-catered</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Self-Catered</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>travel_accommodation_choices</t>
+          <t>travel_food_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>hostel</t>
+          <t>packaged</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hostel</t>
+          <t>Packaged</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>travel_accommodation_choices</t>
+          <t>travel_food_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>travel_food_choices</t>
+          <t>travel_water_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2530,58 +2530,58 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>travel_food_choices</t>
+          <t>travel_water_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>self-catered</t>
+          <t>tap_water</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Self-Catered</t>
+          <t>Tap Water</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>travel_food_choices</t>
+          <t>travel_water_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>packaged</t>
+          <t>bottled</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Packaged</t>
+          <t>Bottled</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>travel_food_choices</t>
+          <t>travel_water_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>travel_water_choices</t>
+          <t>travel_safety_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2598,51 +2598,51 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>travel_water_choices</t>
+          <t>travel_safety_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>tap_water</t>
+          <t>hand_sanitizer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tap Water</t>
+          <t>Hand Sanitizer</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>travel_water_choices</t>
+          <t>travel_safety_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>bottled</t>
+          <t>face_mask</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bottled</t>
+          <t>Face Mask</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>travel_water_choices</t>
+          <t>travel_safety_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>social_distancing</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Social Distancing</t>
         </is>
       </c>
     </row>
@@ -2654,80 +2654,80 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>travel_safety_choices</t>
+          <t>travel_safety_measures_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>hand_sanitizer</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hand Sanitizer</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>travel_safety_choices</t>
+          <t>travel_safety_measures_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>face_mask</t>
+          <t>temperature_check</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Face Mask</t>
+          <t>Temperature Check</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>travel_safety_choices</t>
+          <t>travel_safety_measures_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>social_distancing</t>
+          <t>mask_mandate</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Social Distancing</t>
+          <t>Mask Mandate</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>travel_safety_choices</t>
+          <t>travel_safety_measures_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>contact_tracing</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Contact Tracing</t>
         </is>
       </c>
     </row>
@@ -2739,80 +2739,80 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>travel_safety_measures_choices</t>
+          <t>travel_safety_equipment_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>temperature_check</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Temperature Check</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>travel_safety_measures_choices</t>
+          <t>travel_safety_equipment_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>mask_mandate</t>
+          <t>thermometer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Mask Mandate</t>
+          <t>Thermometer</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>travel_safety_measures_choices</t>
+          <t>travel_safety_equipment_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>contact_tracing</t>
+          <t>hand_gloves</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Contact Tracing</t>
+          <t>Hand Gloves</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>travel_safety_measures_choices</t>
+          <t>travel_safety_equipment_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>face_shield</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Face Shield</t>
         </is>
       </c>
     </row>
@@ -2824,78 +2824,10 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>travel_safety_equipment_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>thermometer</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Thermometer</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>travel_safety_equipment_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>hand_gloves</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Hand Gloves</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>travel_safety_equipment_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>face_shield</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Face Shield</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>travel_safety_equipment_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
